--- a/Mantenimiento/excels/CAJAMARCA-SAN_MARCOS-PEDRO_GALVEZ.xlsx
+++ b/Mantenimiento/excels/CAJAMARCA-SAN_MARCOS-PEDRO_GALVEZ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -503,12 +498,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -535,11 +530,6 @@
       </c>
       <c r="K2" t="n">
         <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -555,12 +545,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -587,11 +577,6 @@
       </c>
       <c r="K3" t="n">
         <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -607,12 +592,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -639,11 +624,6 @@
       </c>
       <c r="K4" t="n">
         <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -659,12 +639,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -691,11 +671,6 @@
       </c>
       <c r="K5" t="n">
         <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -711,12 +686,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -743,11 +718,6 @@
       </c>
       <c r="K6" t="n">
         <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -763,12 +733,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -795,11 +765,6 @@
       </c>
       <c r="K7" t="n">
         <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="8">
@@ -815,12 +780,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -847,11 +812,6 @@
       </c>
       <c r="K8" t="n">
         <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -867,12 +827,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -899,11 +859,6 @@
       </c>
       <c r="K9" t="n">
         <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="10">
@@ -919,12 +874,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SAN_MARCOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PEDRO_GALVEZ</t>
+          <t>PEDRO GALVEZ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -951,11 +906,6 @@
       </c>
       <c r="K10" t="n">
         <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Mantenimiento/excels/CAJAMARCA-SAN_MARCOS-PEDRO_GALVEZ.xlsx
+++ b/Mantenimiento/excels/CAJAMARCA-SAN_MARCOS-PEDRO_GALVEZ.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
@@ -516,20 +504,30 @@
           <t>012</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-7.334965</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-78.166909</v>
-      </c>
-      <c r="I2" t="n">
-        <v>173</v>
-      </c>
-      <c r="J2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-7.334965</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-78.166909</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -563,20 +561,30 @@
           <t>163</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-7.334066</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-78.17276200000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>124</v>
-      </c>
-      <c r="J3" t="n">
-        <v>6</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-7.334066</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-78.172762</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -610,20 +618,30 @@
           <t>190</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-7.332661</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-78.170286</v>
-      </c>
-      <c r="I4" t="n">
-        <v>61</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-7.332661</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-78.170286</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -657,20 +675,30 @@
           <t>82081 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-7.335753</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-78.169732</v>
-      </c>
-      <c r="I5" t="n">
-        <v>468</v>
-      </c>
-      <c r="J5" t="n">
-        <v>23</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-7.335753</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-78.169732</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -704,20 +732,30 @@
           <t>82952 DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-7.335843</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-78.1661</v>
-      </c>
-      <c r="I6" t="n">
-        <v>426</v>
-      </c>
-      <c r="J6" t="n">
-        <v>23</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-7.335843</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-78.1661</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -751,20 +789,30 @@
           <t>83007 PATRON SAN MARCOS</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-7.336823</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-78.170739</v>
-      </c>
-      <c r="I7" t="n">
-        <v>422</v>
-      </c>
-      <c r="J7" t="n">
-        <v>25</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-7.336823</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-78.170739</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -798,20 +846,30 @@
           <t>SAN MARCOS</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-7.335583</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-78.166876</v>
-      </c>
-      <c r="I8" t="n">
-        <v>821</v>
-      </c>
-      <c r="J8" t="n">
-        <v>62</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-7.335583</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-78.166876</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -845,20 +903,30 @@
           <t>SAN MARCOS APOSTOL</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-7.33562</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-78.16981</v>
-      </c>
-      <c r="I9" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-7.33562</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-78.16981</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -892,20 +960,30 @@
           <t>JESUS DE NAZARET</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-7.33606</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-78.17001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-7.33606</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-78.17001</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
